--- a/frontend/config/render-config.xlsx
+++ b/frontend/config/render-config.xlsx
@@ -1624,7 +1624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K123"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1700,6 +1700,11 @@
           <t>light_color_temp</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="72" t="inlineStr">
@@ -6506,6 +6511,307 @@
       <c r="H123" s="78" t="inlineStr">
         <is>
           <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>restrictions</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>preserve[]</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>preserve</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>geometria_camara</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>geometría, cámara y relación de aspecto exactas de la imagen</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>exact geometry, camera viewpoint and aspect ratio of the input image</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>restrictions</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>preserve[]</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>preserve</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>contexto_blanco</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>volúmenes blancos de contexto neutros y secundarios</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>white context volumes kept neutral and secondary</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>restrictions</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>preserve[]</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>preserve</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>trazado_calles</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>trazado de calles, accesos y topografía de fondo</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>street layout, accesses and background topography</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>restrictions</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>preserve[]</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>preserve</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>vegetacion_estructural</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>distribución estructural de la vegetación existente</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>structural distribution of the existing vegetation</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>restrictions</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>preserve[]</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>preserve</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>materiales_verticales</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>materiales mate y realistas, verticales corregidas</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>materials matte and true-to-life, corrected verticals</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>restrictions</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>avoid[]</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>avoid</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>vegetacion_tropical</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>vegetación tropical o palmeras</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>tropical vegetation or palm trees</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>restrictions</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>avoid[]</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>avoid</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>gloss_inmobiliario</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>brillo inmobiliario comercial o sobresaturación</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>commercial real-estate gloss or oversaturation</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>

--- a/frontend/config/render-config.xlsx
+++ b/frontend/config/render-config.xlsx
@@ -1624,7 +1624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:L133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6530,7 +6530,6 @@
           <t>preserve</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>geometria_camara</t>
@@ -6573,7 +6572,6 @@
           <t>preserve</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>contexto_blanco</t>
@@ -6616,7 +6614,6 @@
           <t>preserve</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>trazado_calles</t>
@@ -6659,7 +6656,6 @@
           <t>preserve</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>vegetacion_estructural</t>
@@ -6702,7 +6698,6 @@
           <t>preserve</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>materiales_verticales</t>
@@ -6745,7 +6740,6 @@
           <t>avoid</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>vegetacion_tropical</t>
@@ -6788,7 +6782,6 @@
           <t>avoid</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>gloss_inmobiliario</t>
@@ -6814,6 +6807,123 @@
           <t>TRUE</t>
         </is>
       </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>locked.role</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>forma</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>render de Forma</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Autodesk Forma color-coded massing: each flat color is a USE, not a final material</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>locked.role</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>sketchup</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>render de SketchUp</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>SketchUp color-coded massing: each flat color is a USE, not a final material</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>locked.role</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>rhino</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>render de Rhino</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Rhino color-coded massing: each flat color is a USE, not a final material</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
